--- a/inspection_forms/032_snow_removal_site_inspection_form--inspection_forms.xlsx
+++ b/inspection_forms/032_snow_removal_site_inspection_form--inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'light',_'value':_'light'}</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Light', 'value': 'Light'}</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium', 'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'heavy',_'value':_'heavy'}</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Heavy', 'value': 'Heavy'}</t>
+          <t>Heavy</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'plowing',_'value':_'plowing'}</t>
+          <t>plowing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Plowing', 'value': 'Plowing'}</t>
+          <t>Plowing</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'salting',_'value':_'salting'}</t>
+          <t>salting</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Salting', 'value': 'Salting'}</t>
+          <t>Salting</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Both', 'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'neither',_'value':_'neither'}</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Neither', 'value': 'Neither'}</t>
+          <t>Neither</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'driveway',_'value':_'driveway'}</t>
+          <t>driveway</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Driveway', 'value': 'Driveway'}</t>
+          <t>Driveway</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'sidewalk',_'value':_'sidewalk'}</t>
+          <t>sidewalk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Sidewalk', 'value': 'Sidewalk'}</t>
+          <t>Sidewalk</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'parking_lot',_'value':_'parking_lot'}</t>
+          <t>parking_lot</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Parking lot', 'value': 'Parking lot'}</t>
+          <t>Parking lot</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'sidewalk_and_driveway',_'value':_'sidewalk_and_driveway'}</t>
+          <t>sidewalk_and_driveway</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Sidewalk and Driveway', 'value': 'Sidewalk and Driveway'}</t>
+          <t>Sidewalk and Driveway</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
